--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260709.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260709.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.78%</t>
+          <t>10.51%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>4,597,000</t>
+          <t>4,653,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.94%</t>
+          <t>8.97%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.18%</t>
+          <t>8.22%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.50%</t>
+          <t>7.33%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.77%</t>
+          <t>6.30%</t>
         </is>
       </c>
     </row>
@@ -726,95 +726,95 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>5.69%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>86,550,000</t>
+          <t>15,779,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.16%</t>
+          <t>5.03%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>15,203,000</t>
+          <t>86,550,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.80%</t>
+          <t>4.91%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,417,000</t>
+          <t>5,191,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>4.44%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>5,191,000</t>
+          <t>2,417,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>4.43%</t>
         </is>
       </c>
     </row>
@@ -831,34 +831,34 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>8,949,000</t>
+          <t>9,149,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>4.05%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>8,315,000</t>
+          <t>14,770,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.64%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.46%</t>
         </is>
       </c>
     </row>
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.28%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,160,000</t>
+          <t>8,315,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>12,742,000</t>
+          <t>5,160,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1100,51 +1100,51 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>3,528,000</t>
+          <t>411,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>411,000</t>
+          <t>3,528,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1298,46 +1298,46 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>4,369,542,800</t>
+          <t>4,510,225,108</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-692,265,646</t>
+          <t>-2,837,476,642</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
